--- a/TENX.xlsx
+++ b/TENX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C617172B-F57C-40CB-A6B7-BF87173A0504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CAD5012-7D6E-491F-8219-B241F219C30A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28065" yWindow="1545" windowWidth="25080" windowHeight="18540" xr2:uid="{BBC30BB9-D7B0-4373-B99D-63A7B7F28A5A}"/>
+    <workbookView xWindow="14690" yWindow="2940" windowWidth="22360" windowHeight="16580" xr2:uid="{BBC30BB9-D7B0-4373-B99D-63A7B7F28A5A}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>Price</t>
   </si>
@@ -91,13 +91,31 @@
   </si>
   <si>
     <t>inotrope</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Clinical Trials</t>
+  </si>
+  <si>
+    <t>Phase III "LEVEL-2"</t>
+  </si>
+  <si>
+    <t>Q326 results</t>
+  </si>
+  <si>
+    <t>Phase II "HELP"</t>
+  </si>
+  <si>
+    <t>Phase III "LEVEL" PH-HFpEF</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -111,6 +129,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -226,7 +252,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -236,6 +261,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -574,102 +600,88 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEEE195F-F999-4BE3-B0C3-EDF3322A6CCD}">
   <dimension ref="B2:L7"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.5703125" customWidth="1"/>
+    <col min="1" max="1" width="3.54296875" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B2" s="9" t="s">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="11"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="10"/>
       <c r="J2" t="s">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>6.41</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B3" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
+      <c r="H3" s="4"/>
       <c r="J3" t="s">
         <v>1</v>
       </c>
       <c r="K3" s="1">
-        <f>3.408906+31.882671</f>
-        <v>35.291576999999997</v>
+        <v>26.525158999999999</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="4"/>
       <c r="J4" t="s">
         <v>2</v>
       </c>
       <c r="K4" s="1">
         <f>+K2*K3</f>
-        <v>226.21900856999997</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
+        <v>477.45286199999998</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="5"/>
+      <c r="H5" s="4"/>
       <c r="J5" t="s">
         <v>3</v>
       </c>
       <c r="K5" s="1">
-        <v>98.310918000000001</v>
+        <v>118.755</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B6" s="6"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="8"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B6" s="5"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="7"/>
       <c r="J6" t="s">
         <v>4</v>
       </c>
@@ -680,13 +692,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="J7" t="s">
         <v>5</v>
       </c>
       <c r="K7" s="1">
         <f>+K4-K5+K6</f>
-        <v>127.90809056999997</v>
+        <v>358.69786199999999</v>
       </c>
     </row>
   </sheetData>
@@ -699,23 +711,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2538E0D7-C9CE-48E6-A4BE-0BCC3561E401}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>15</v>
       </c>
@@ -723,12 +736,37 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>11</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C6" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C11" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C14" s="13" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
